--- a/data/trans_orig/P57B4_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B4_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha tenido la sensación de disfrutar de la vida en 2023</t>
+          <t>Población según si ha tenido la sensación de disfrutar de la vida en 2023 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119979</t>
+          <t>121880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>159215</t>
+          <t>159109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138054</t>
+          <t>136826</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171827</t>
+          <t>171997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>269127</t>
+          <t>266156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321323</t>
+          <t>317553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224563</t>
+          <t>224341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268938</t>
+          <t>265196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>332462</t>
+          <t>336110</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>374254</t>
+          <t>376932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>572052</t>
+          <t>571851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>631264</t>
+          <t>636573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86660</t>
+          <t>87097</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118381</t>
+          <t>118169</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>169973</t>
+          <t>170296</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208227</t>
+          <t>209657</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>263327</t>
+          <t>264814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>314161</t>
+          <t>313258</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30803</t>
+          <t>31924</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33051</t>
+          <t>33483</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53117</t>
+          <t>52016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52549</t>
+          <t>52427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76733</t>
+          <t>76083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1045814</t>
+          <t>1040758</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1507411</t>
+          <t>1534589</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>787994</t>
+          <t>782933</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1331377</t>
+          <t>1271681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2138265</t>
+          <t>2138266</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1867494</t>
+          <t>1877469</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2607229</t>
+          <t>2611105</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>599869</t>
+          <t>570109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>950712</t>
+          <t>955942</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>695821</t>
+          <t>737692</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1124423</t>
+          <t>1123508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1816588</t>
+          <t>1816589</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1447395</t>
+          <t>1466419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2044948</t>
+          <t>2033098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150702</t>
+          <t>146354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>258015</t>
+          <t>258304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>181252</t>
+          <t>183413</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291078</t>
+          <t>291581</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>375634</t>
+          <t>369987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>530591</t>
+          <t>527281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>51396</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37952</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69185</t>
+          <t>68325</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>67662</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110245</t>
+          <t>111975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4511171</t>
+          <t>4511172</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4511171</t>
+          <t>4511172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4511171</t>
+          <t>4511172</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262912</t>
+          <t>260138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>319046</t>
+          <t>316126</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>269846</t>
+          <t>268686</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>314031</t>
+          <t>313265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>543961</t>
+          <t>549091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>617950</t>
+          <t>620082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>245503</t>
+          <t>245321</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>299288</t>
+          <t>299766</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>260130</t>
+          <t>262366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304753</t>
+          <t>308568</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>520435</t>
+          <t>518626</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>588338</t>
+          <t>585991</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50112</t>
+          <t>51219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81507</t>
+          <t>84044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57977</t>
+          <t>59094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83818</t>
+          <t>84341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117060</t>
+          <t>115158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157991</t>
+          <t>157414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52880</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19911</t>
+          <t>19120</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60635</t>
+          <t>66995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1461931</t>
+          <t>1466268</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2029866</t>
+          <t>2013191</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1224756</t>
+          <t>1231348</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1767576</t>
+          <t>1892921</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2750041</t>
+          <t>2741474</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3642908</t>
+          <t>3563223</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>50,45%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1034098</t>
+          <t>1059556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1480195</t>
+          <t>1473686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1346742</t>
+          <t>1283677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1760404</t>
+          <t>1757219</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2530797</t>
+          <t>2569859</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3201768</t>
+          <t>3185863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>292063</t>
+          <t>299120</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>431536</t>
+          <t>432560</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>416465</t>
+          <t>414531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>560366</t>
+          <t>560973</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>773544</t>
+          <t>761729</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>965171</t>
+          <t>966461</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58239</t>
+          <t>57161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110414</t>
+          <t>107727</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84616</t>
+          <t>86001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126291</t>
+          <t>125879</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>152927</t>
+          <t>154251</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>221620</t>
+          <t>219536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B4_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B4_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>139628</t>
+          <t>156573</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121880</t>
+          <t>135008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>159109</t>
+          <t>178150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>154489</t>
+          <t>170065</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136826</t>
+          <t>150447</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171997</t>
+          <t>188282</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>294118</t>
+          <t>326638</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266156</t>
+          <t>298310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>317553</t>
+          <t>355491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>245598</t>
+          <t>272403</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224341</t>
+          <t>250772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265196</t>
+          <t>295002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>355434</t>
+          <t>392143</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>336110</t>
+          <t>368306</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>376932</t>
+          <t>413893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>601031</t>
+          <t>664546</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>571851</t>
+          <t>632516</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>636573</t>
+          <t>697268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>101412</t>
+          <t>113201</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87097</t>
+          <t>96834</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118169</t>
+          <t>130865</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>187555</t>
+          <t>197900</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170296</t>
+          <t>179899</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>209657</t>
+          <t>219106</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>288968</t>
+          <t>311101</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>264814</t>
+          <t>287470</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>313258</t>
+          <t>339430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -1064,27 +1064,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>25281</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>17221</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31924</t>
+          <t>35577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41775</t>
+          <t>44541</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33483</t>
+          <t>35710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>55064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>64079</t>
+          <t>69822</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52427</t>
+          <t>57040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76083</t>
+          <t>84082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>508942</t>
+          <t>567458</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>508942</t>
+          <t>567458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508942</t>
+          <t>567458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>739254</t>
+          <t>804648</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>739254</t>
+          <t>804648</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>739254</t>
+          <t>804648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1248196</t>
+          <t>1372106</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1248196</t>
+          <t>1372106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1248196</t>
+          <t>1372106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1194022</t>
+          <t>1029712</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1040758</t>
+          <t>976092</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1534589</t>
+          <t>1086861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>944244</t>
+          <t>836313</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>782933</t>
+          <t>793070</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1271681</t>
+          <t>881407</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2138266</t>
+          <t>1866024</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1877469</t>
+          <t>1797579</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2611105</t>
+          <t>1941690</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>835119</t>
+          <t>913073</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>570109</t>
+          <t>861019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>955942</t>
+          <t>964307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>981470</t>
+          <t>986018</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>737692</t>
+          <t>943424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1123508</t>
+          <t>1028730</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1816589</t>
+          <t>1899091</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1466419</t>
+          <t>1823139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2033098</t>
+          <t>1963687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>216100</t>
+          <t>240236</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146354</t>
+          <t>214114</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>258304</t>
+          <t>274567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>250936</t>
+          <t>281638</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>183413</t>
+          <t>256730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291581</t>
+          <t>311052</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>467036</t>
+          <t>521874</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>369987</t>
+          <t>483022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>527281</t>
+          <t>561059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36822</t>
+          <t>39133</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23737</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51396</t>
+          <t>54639</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52460</t>
+          <t>57017</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>45231</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68325</t>
+          <t>73080</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>89282</t>
+          <t>96150</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67662</t>
+          <t>80371</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>111975</t>
+          <t>116615</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2282063</t>
+          <t>2222154</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2282063</t>
+          <t>2222154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2282063</t>
+          <t>2222154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2229109</t>
+          <t>2160986</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2229109</t>
+          <t>2160986</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2229109</t>
+          <t>2160986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4511172</t>
+          <t>4383140</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4511172</t>
+          <t>4383140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4511172</t>
+          <t>4383140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>290274</t>
+          <t>322698</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>260138</t>
+          <t>295232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>316126</t>
+          <t>352072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>291681</t>
+          <t>323235</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>268686</t>
+          <t>297154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>313265</t>
+          <t>345484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>581955</t>
+          <t>645933</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>549091</t>
+          <t>607314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>620082</t>
+          <t>686215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>271513</t>
+          <t>303127</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>245321</t>
+          <t>271224</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>299766</t>
+          <t>329078</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>284066</t>
+          <t>312421</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>262366</t>
+          <t>290283</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>308568</t>
+          <t>339180</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>555579</t>
+          <t>615548</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>518626</t>
+          <t>578681</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>585991</t>
+          <t>652875</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>65379</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51219</t>
+          <t>55205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>88923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>70160</t>
+          <t>82981</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59094</t>
+          <t>68678</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84341</t>
+          <t>99618</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>135539</t>
+          <t>153537</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115158</t>
+          <t>131499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157414</t>
+          <t>179842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>14605</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53171</t>
+          <t>26253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>22171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>30720</t>
+          <t>28195</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66995</t>
+          <t>41101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646006</t>
+          <t>710986</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646006</t>
+          <t>710986</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646006</t>
+          <t>710986</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>657786</t>
+          <t>732227</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>657786</t>
+          <t>732227</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>657786</t>
+          <t>732227</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1303792</t>
+          <t>1443213</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1303792</t>
+          <t>1443213</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1303792</t>
+          <t>1443213</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1623924</t>
+          <t>1508983</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1466268</t>
+          <t>1439815</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2013191</t>
+          <t>1578899</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1390414</t>
+          <t>1329613</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1231348</t>
+          <t>1269267</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1892921</t>
+          <t>1384211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3014338</t>
+          <t>2838596</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2741474</t>
+          <t>2745545</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3563223</t>
+          <t>2930163</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1352229</t>
+          <t>1488604</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1059556</t>
+          <t>1419605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1473686</t>
+          <t>1551049</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1620969</t>
+          <t>1690581</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1283677</t>
+          <t>1636585</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1757219</t>
+          <t>1748513</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2973198</t>
+          <t>3179185</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2569859</t>
+          <t>3098051</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3185863</t>
+          <t>3264501</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,35%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>382891</t>
+          <t>423992</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>299120</t>
+          <t>388409</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>432560</t>
+          <t>467666</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>508651</t>
+          <t>562520</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>414531</t>
+          <t>523763</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>560973</t>
+          <t>600740</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>891542</t>
+          <t>986512</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>761729</t>
+          <t>935139</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>966461</t>
+          <t>1042986</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>79019</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57161</t>
+          <t>62731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107727</t>
+          <t>96886</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>106114</t>
+          <t>115147</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86001</t>
+          <t>97908</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125879</t>
+          <t>133513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>184081</t>
+          <t>194167</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154251</t>
+          <t>171316</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>219536</t>
+          <t>221026</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3437011</t>
+          <t>3500598</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3437011</t>
+          <t>3500598</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3437011</t>
+          <t>3500598</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3626148</t>
+          <t>3697861</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3626148</t>
+          <t>3697861</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3626148</t>
+          <t>3697861</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7063159</t>
+          <t>7198459</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7063159</t>
+          <t>7198459</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7063159</t>
+          <t>7198459</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
